--- a/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tareas del hogar realizadas por el/la entrevistado/a</t>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,19; 32,01</t>
+          <t>17,33; 33,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 28,77</t>
+          <t>12,01; 27,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,4; 33,6</t>
+          <t>15,8; 33,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,23; 94,03</t>
+          <t>84,68; 94,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,41; 23,74</t>
+          <t>9,33; 22,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 25,07</t>
+          <t>10,21; 25,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,83; 35,4</t>
+          <t>19,25; 36,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82,87; 92,15</t>
+          <t>82,84; 92,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,28; 25,4</t>
+          <t>14,88; 25,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,8; 23,43</t>
+          <t>12,9; 23,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,55; 31,73</t>
+          <t>19,86; 31,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,45; 92,02</t>
+          <t>85,28; 92,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,23; 35,75</t>
+          <t>18,61; 35,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,96; 37,39</t>
+          <t>18,84; 36,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,29; 40,77</t>
+          <t>24,43; 40,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83,24; 94,3</t>
+          <t>82,67; 94,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,92; 46,06</t>
+          <t>27,18; 46,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,1; 40,22</t>
+          <t>22,67; 40,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,47; 43,23</t>
+          <t>27,31; 42,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,77; 94,28</t>
+          <t>84,68; 94,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,29; 38,2</t>
+          <t>25,69; 38,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,26; 36,36</t>
+          <t>23,23; 35,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,97; 39,1</t>
+          <t>28,31; 39,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,22; 93,55</t>
+          <t>86,11; 93,56</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 18,81</t>
+          <t>5,87; 18,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,96; 31,48</t>
+          <t>14,26; 30,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 27,6</t>
+          <t>9,02; 26,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,87; 82,83</t>
+          <t>61,95; 83,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,89; 32,11</t>
+          <t>16,86; 31,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,02; 28,42</t>
+          <t>12,7; 29,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 24,77</t>
+          <t>9,3; 25,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65,87; 86,16</t>
+          <t>64,05; 85,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,66; 24,65</t>
+          <t>13,64; 24,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 27,06</t>
+          <t>15,46; 27,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,41; 23,3</t>
+          <t>11,2; 22,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,87; 82,62</t>
+          <t>67,73; 82,58</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,37; 40,08</t>
+          <t>28,04; 40,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,79; 41,55</t>
+          <t>28,16; 41,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,72; 39,24</t>
+          <t>27,96; 39,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,99; 89,42</t>
+          <t>74,65; 89,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 36,32</t>
+          <t>23,55; 35,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 36,33</t>
+          <t>23,49; 36,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,25; 36,23</t>
+          <t>24,25; 36,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,31; 91,59</t>
+          <t>83,06; 91,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,49; 36,15</t>
+          <t>27,2; 35,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,49; 36,27</t>
+          <t>27,28; 36,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,57; 36,19</t>
+          <t>27,76; 35,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,56; 88,81</t>
+          <t>80,84; 89,26</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,48; 59,5</t>
+          <t>38,92; 58,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,65; 48,66</t>
+          <t>32,41; 49,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,2; 46,33</t>
+          <t>31,01; 46,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,84; 94,13</t>
+          <t>83,98; 93,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 59,89</t>
+          <t>43,8; 60,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,14; 62,42</t>
+          <t>44,27; 61,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,05; 53,18</t>
+          <t>36,23; 53,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,61; 89,88</t>
+          <t>78,59; 89,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,56; 57,16</t>
+          <t>43,95; 56,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,79; 52,93</t>
+          <t>40,64; 52,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,87; 46,68</t>
+          <t>35,48; 46,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>82,74; 89,98</t>
+          <t>82,55; 90,19</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,21; 73,75</t>
+          <t>56,3; 74,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52,58; 73,28</t>
+          <t>53,06; 74,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,47; 54,67</t>
+          <t>32,83; 53,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76,96; 91,33</t>
+          <t>77,53; 91,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54,6; 72,42</t>
+          <t>54,79; 72,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,86; 58,9</t>
+          <t>41,17; 59,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,59; 54,86</t>
+          <t>35,08; 55,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75,71; 91,99</t>
+          <t>77,07; 92,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57,45; 70,51</t>
+          <t>58,29; 71,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47,99; 63,19</t>
+          <t>48,7; 63,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36,88; 51,37</t>
+          <t>37,12; 51,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78,77; 90,1</t>
+          <t>79,05; 89,87</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,15; 38,9</t>
+          <t>31,89; 38,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,84; 37,98</t>
+          <t>30,61; 37,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,07</t>
+          <t>29,39; 35,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,64; 88,65</t>
+          <t>82,7; 88,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,55; 39,17</t>
+          <t>32,64; 39,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,39; 36,96</t>
+          <t>30,53; 36,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,71; 36,16</t>
+          <t>30,06; 36,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,04; 88,71</t>
+          <t>84,14; 88,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,25; 38,1</t>
+          <t>33,35; 38,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,64; 36,42</t>
+          <t>31,59; 36,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,77; 35,3</t>
+          <t>30,34; 35,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,25; 87,89</t>
+          <t>84,35; 88,14</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>19393</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11779</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15653</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>93955</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10840</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12230</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20773</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>121073</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>30233</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24009</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>36426</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>215027</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>13944; 26808</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7355; 17002</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10242; 21782</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88463; 98285</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6682; 16046</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7497; 18383</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15066; 28197</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>113419; 127314</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>22634; 38410</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17373; 31979</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>28411; 45412</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>205836; 223209</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>18093</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18013</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26411</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85240</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24512</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21085</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32301</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>86163</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>42605</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>39098</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>58712</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>171404</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12785; 24321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12318; 24083</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20105; 33557</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>78270; 89086</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>18341; 31163</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>15537; 28050</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>25421; 39636</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>80930; 90370</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>34977; 51921</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>31102; 47862</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>49655; 69269</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>163823; 178006</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6540</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14705</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38229</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19808</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13338</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9915</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>49323</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>26349</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28043</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18127</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>87552</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3417; 11056</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9489; 20317</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4442; 13259</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32126; 43058</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14151; 26245</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8634; 20055</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5675; 15591</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>40899; 54822</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>19401; 34560</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>20785; 36455</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12350; 25274</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>78372; 95555</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>51258</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47198</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55775</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>181605</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43640</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47758</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51180</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>192026</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>94898</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>94956</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>106955</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>373631</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>42420; 60996</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38428; 57135</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>46352; 65430</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163356; 195352</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>34989; 52981</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>37902; 58190</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>41446; 61719</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>181297; 199604</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>81563; 107358</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>81241; 107323</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>93470; 121175</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>353341; 390167</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>33588</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>37935</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>38725</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>107344</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>43900</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48679</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44394</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>137804</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>77488</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>86614</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>83119</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>245148</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>26900; 40224</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30284; 46516</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31502; 47316</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>100301; 112008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>37025; 51259</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>40728; 56859</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>35927; 52701</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>127798; 145410</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>67528; 87037</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>75370; 98243</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>71216; 94271</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>232838; 254380</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>49167</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>34305</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>26209</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>58783</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>45981</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>37304</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>30370</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>61529</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>95148</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>71608</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>56579</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>120312</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>42151; 55786</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>28608; 40248</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>19806; 32335</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>53416; 63137</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>39667; 52240</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>30483; 44343</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>23796; 37765</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>55491; 66382</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>85838; 104684</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>62313; 81373</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>47571; 66124</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>111381; 126622</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>178038</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>163934</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>170985</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>565157</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>180395</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>647916</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>366722</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>344329</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>359917</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1213073</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>160322; 195946</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>146023; 180617</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>154008; 187285</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>544312; 582696</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>172522; 206363</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>164037; 198568</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>171398; 206715</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>630431; 664457</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>343957; 392820</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>320438; 368067</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>332007; 385208</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1187100; 1240477</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,33; 33,32</t>
+          <t>16,8; 33,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,01; 27,77</t>
+          <t>12,25; 28,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 33,6</t>
+          <t>16,63; 35,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,68; 94,09</t>
+          <t>84,28; 94,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 22,4</t>
+          <t>9,15; 22,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,21; 25,04</t>
+          <t>10,55; 24,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,25; 36,03</t>
+          <t>18,65; 36,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82,84; 92,99</t>
+          <t>83,19; 92,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 25,25</t>
+          <t>15,07; 25,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,9; 23,75</t>
+          <t>12,9; 23,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,86; 31,74</t>
+          <t>19,79; 31,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,28; 92,48</t>
+          <t>85,0; 92,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,61; 35,41</t>
+          <t>18,25; 35,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,84; 36,84</t>
+          <t>18,08; 36,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,43; 40,77</t>
+          <t>24,67; 41,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,67; 94,09</t>
+          <t>84,2; 94,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,18; 46,18</t>
+          <t>26,99; 46,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 40,93</t>
+          <t>23,02; 41,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,31; 42,59</t>
+          <t>27,13; 42,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,68; 94,56</t>
+          <t>84,24; 94,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,69; 38,13</t>
+          <t>24,88; 37,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 35,74</t>
+          <t>23,03; 35,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,31; 39,5</t>
+          <t>28,01; 39,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,11; 93,56</t>
+          <t>85,95; 93,35</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 18,98</t>
+          <t>5,93; 19,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 30,54</t>
+          <t>14,79; 30,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 26,94</t>
+          <t>9,52; 27,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,95; 83,03</t>
+          <t>61,17; 82,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,86; 31,27</t>
+          <t>16,41; 31,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,7; 29,51</t>
+          <t>12,58; 28,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 25,55</t>
+          <t>9,43; 25,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,05; 85,86</t>
+          <t>63,25; 85,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,64; 24,31</t>
+          <t>13,92; 24,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,46; 27,11</t>
+          <t>15,86; 27,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,2; 22,93</t>
+          <t>11,38; 22,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,73; 82,58</t>
+          <t>67,4; 82,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,04; 40,32</t>
+          <t>28,04; 40,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,16; 41,86</t>
+          <t>28,21; 41,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,96; 39,46</t>
+          <t>27,3; 39,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,65; 89,27</t>
+          <t>74,51; 89,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,55; 35,66</t>
+          <t>23,65; 35,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,49; 36,06</t>
+          <t>23,54; 35,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,25; 36,12</t>
+          <t>24,27; 35,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,06; 91,45</t>
+          <t>83,55; 91,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,2; 35,8</t>
+          <t>27,26; 36,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,28; 36,03</t>
+          <t>27,6; 36,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,76; 35,99</t>
+          <t>27,75; 35,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,84; 89,26</t>
+          <t>80,87; 89,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,92; 58,19</t>
+          <t>40,15; 59,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,41; 49,78</t>
+          <t>32,65; 49,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,01; 46,58</t>
+          <t>30,27; 46,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83,98; 93,79</t>
+          <t>85,07; 94,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,8; 60,64</t>
+          <t>44,53; 60,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,27; 61,8</t>
+          <t>43,94; 61,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,23; 53,15</t>
+          <t>36,64; 53,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,59; 89,42</t>
+          <t>78,74; 89,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,95; 56,65</t>
+          <t>44,47; 56,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,64; 52,97</t>
+          <t>40,81; 52,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,48; 46,96</t>
+          <t>35,5; 46,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>82,55; 90,19</t>
+          <t>83,08; 90,31</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56,3; 74,51</t>
+          <t>55,76; 73,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,06; 74,66</t>
+          <t>51,46; 74,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,83; 53,59</t>
+          <t>34,03; 53,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77,53; 91,64</t>
+          <t>76,24; 91,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54,79; 72,16</t>
+          <t>53,46; 72,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,17; 59,89</t>
+          <t>41,8; 60,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,08; 55,68</t>
+          <t>35,24; 55,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>77,07; 92,19</t>
+          <t>76,25; 92,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58,29; 71,09</t>
+          <t>58,5; 70,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,7; 63,6</t>
+          <t>48,89; 63,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37,12; 51,6</t>
+          <t>37,21; 52,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79,05; 89,87</t>
+          <t>79,08; 90,16</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,89; 38,98</t>
+          <t>32,1; 38,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,61; 37,87</t>
+          <t>31,15; 38,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,39; 35,74</t>
+          <t>29,23; 35,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,7; 88,54</t>
+          <t>82,46; 88,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,64; 39,04</t>
+          <t>32,32; 39,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,53; 36,96</t>
+          <t>30,12; 36,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,06; 36,25</t>
+          <t>29,62; 36,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,14; 88,69</t>
+          <t>83,93; 88,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,35; 38,09</t>
+          <t>33,35; 38,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,59; 36,29</t>
+          <t>31,66; 36,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,34; 35,2</t>
+          <t>30,61; 35,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,35; 88,14</t>
+          <t>84,14; 87,93</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13944; 26808</t>
+          <t>13519; 27061</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7355; 17002</t>
+          <t>7500; 17258</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10242; 21782</t>
+          <t>10778; 22813</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88463; 98285</t>
+          <t>88036; 98293</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6682; 16046</t>
+          <t>6558; 16210</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7497; 18383</t>
+          <t>7745; 18205</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15066; 28197</t>
+          <t>14591; 28828</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113419; 127314</t>
+          <t>113895; 127313</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22634; 38410</t>
+          <t>22918; 38851</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17373; 31979</t>
+          <t>17370; 32089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28411; 45412</t>
+          <t>28311; 45091</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>205836; 223209</t>
+          <t>205166; 222729</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12785; 24321</t>
+          <t>12533; 24254</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12318; 24083</t>
+          <t>11823; 23953</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20105; 33557</t>
+          <t>20309; 34230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78270; 89086</t>
+          <t>79721; 89104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18341; 31163</t>
+          <t>18217; 31334</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15537; 28050</t>
+          <t>15777; 28460</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25421; 39636</t>
+          <t>25253; 39985</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80930; 90370</t>
+          <t>80511; 90269</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34977; 51921</t>
+          <t>33877; 51688</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31102; 47862</t>
+          <t>30836; 47658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49655; 69269</t>
+          <t>49126; 68824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>163823; 178006</t>
+          <t>163523; 177602</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3417; 11056</t>
+          <t>3454; 11450</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9489; 20317</t>
+          <t>9840; 20436</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4442; 13259</t>
+          <t>4688; 13369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32126; 43058</t>
+          <t>31725; 42905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14151; 26245</t>
+          <t>13775; 26355</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8634; 20055</t>
+          <t>8551; 19284</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5675; 15591</t>
+          <t>5751; 15382</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40899; 54822</t>
+          <t>40386; 54473</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19401; 34560</t>
+          <t>19799; 34712</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20785; 36455</t>
+          <t>21335; 36548</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12350; 25274</t>
+          <t>12547; 25226</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78372; 95555</t>
+          <t>77994; 95476</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42420; 60996</t>
+          <t>42422; 61022</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38428; 57135</t>
+          <t>38502; 57108</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46352; 65430</t>
+          <t>45258; 65227</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163356; 195352</t>
+          <t>163053; 195570</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34989; 52981</t>
+          <t>35132; 52971</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37902; 58190</t>
+          <t>37983; 57636</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41446; 61719</t>
+          <t>41474; 60468</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>181297; 199604</t>
+          <t>182370; 200048</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81563; 107358</t>
+          <t>81752; 108099</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81241; 107323</t>
+          <t>82194; 108703</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93470; 121175</t>
+          <t>93439; 120838</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>353341; 390167</t>
+          <t>353478; 389021</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26900; 40224</t>
+          <t>27755; 40841</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30284; 46516</t>
+          <t>30508; 46005</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31502; 47316</t>
+          <t>30747; 47373</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100301; 112008</t>
+          <t>101602; 112507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37025; 51259</t>
+          <t>37638; 51285</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40728; 56859</t>
+          <t>40427; 56438</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35927; 52701</t>
+          <t>36329; 53066</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>127798; 145410</t>
+          <t>128050; 145172</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67528; 87037</t>
+          <t>68336; 87160</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75370; 98243</t>
+          <t>75680; 98082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71216; 94271</t>
+          <t>71259; 93805</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>232838; 254380</t>
+          <t>234331; 254727</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42151; 55786</t>
+          <t>41751; 55389</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28608; 40248</t>
+          <t>27744; 40417</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19806; 32335</t>
+          <t>20532; 32416</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53416; 63137</t>
+          <t>52524; 62754</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39667; 52240</t>
+          <t>38700; 52463</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30483; 44343</t>
+          <t>30950; 44511</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23796; 37765</t>
+          <t>23902; 37645</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55491; 66382</t>
+          <t>54905; 66241</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85838; 104684</t>
+          <t>86156; 104466</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62313; 81373</t>
+          <t>62557; 80606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47571; 66124</t>
+          <t>47691; 66735</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>111381; 126622</t>
+          <t>111429; 127041</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>160322; 195946</t>
+          <t>161367; 194835</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>146023; 180617</t>
+          <t>148578; 181319</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>154008; 187285</t>
+          <t>153190; 187269</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>544312; 582696</t>
+          <t>542711; 582449</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>172522; 206363</t>
+          <t>170832; 207188</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>164037; 198568</t>
+          <t>161831; 198110</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>171398; 206715</t>
+          <t>168905; 206654</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>630431; 664457</t>
+          <t>628852; 663625</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>343957; 392820</t>
+          <t>343905; 391851</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>320438; 368067</t>
+          <t>321149; 367570</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>332007; 385208</t>
+          <t>334985; 388354</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1187100; 1240477</t>
+          <t>1184200; 1237576</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26,55%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>87,43%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24,1%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19,24%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>24,14%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89,94%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,55%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,8; 33,64</t>
+          <t>9,41; 23,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 28,19</t>
+          <t>10,39; 25,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,63; 35,19</t>
+          <t>18,83; 35,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,28; 94,09</t>
+          <t>81,3; 91,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 22,63</t>
+          <t>17,19; 32,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 24,8</t>
+          <t>12,14; 28,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,65; 36,84</t>
+          <t>16,4; 33,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,19; 92,99</t>
+          <t>84,43; 94,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,07; 25,54</t>
+          <t>15,28; 25,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,9; 23,83</t>
+          <t>12,8; 23,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,79; 31,51</t>
+          <t>19,55; 31,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,0; 92,28</t>
+          <t>85,06; 91,94</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36,32%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30,77%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>26,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>27,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>32,09%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>90,03%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,71%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,25; 35,31</t>
+          <t>27,92; 46,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,08; 36,64</t>
+          <t>22,1; 40,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,67; 41,59</t>
+          <t>27,47; 43,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,2; 94,11</t>
+          <t>83,09; 94,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,99; 46,43</t>
+          <t>18,23; 35,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,02; 41,53</t>
+          <t>19,96; 37,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,13; 42,96</t>
+          <t>24,29; 40,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,24; 94,45</t>
+          <t>82,81; 94,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,88; 37,96</t>
+          <t>25,29; 38,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,03; 35,59</t>
+          <t>23,26; 36,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,01; 39,24</t>
+          <t>27,97; 39,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,95; 93,35</t>
+          <t>85,7; 93,44</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23,6%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,63%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79,7%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11,23%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22,1%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16,68%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 19,66</t>
+          <t>16,89; 32,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,79; 30,72</t>
+          <t>12,02; 28,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,52; 27,16</t>
+          <t>9,66; 24,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,17; 82,73</t>
+          <t>69,16; 88,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 31,4</t>
+          <t>5,65; 18,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,58; 28,37</t>
+          <t>14,96; 31,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 25,21</t>
+          <t>9,7; 27,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,25; 85,31</t>
+          <t>60,95; 82,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,92; 24,41</t>
+          <t>13,66; 24,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,86; 27,18</t>
+          <t>16,04; 27,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 22,88</t>
+          <t>11,41; 23,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,4; 82,51</t>
+          <t>69,78; 83,34</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87,14%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>33,88%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>34,58%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>33,64%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>82,99%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,04; 40,33</t>
+          <t>23,8; 36,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,21; 41,84</t>
+          <t>23,79; 36,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,3; 39,34</t>
+          <t>24,25; 36,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,51; 89,37</t>
+          <t>81,92; 90,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 35,66</t>
+          <t>27,37; 40,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,54; 35,72</t>
+          <t>27,79; 41,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,27; 35,39</t>
+          <t>27,72; 39,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,55; 91,65</t>
+          <t>81,32; 89,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,26; 36,05</t>
+          <t>27,49; 36,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,6; 36,5</t>
+          <t>27,49; 36,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,75; 35,89</t>
+          <t>27,57; 36,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,87; 89,0</t>
+          <t>83,28; 89,25</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>51,93%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>44,77%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>83,94%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>48,59%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>40,59%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>38,12%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>89,88%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>44,77%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,15; 59,08</t>
+          <t>43,07; 59,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,65; 49,23</t>
+          <t>44,14; 62,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,27; 46,64</t>
+          <t>37,05; 53,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,07; 94,2</t>
+          <t>77,56; 88,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,53; 60,67</t>
+          <t>39,48; 59,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,94; 61,34</t>
+          <t>32,65; 48,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,64; 53,52</t>
+          <t>31,2; 46,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,74; 89,27</t>
+          <t>84,7; 94,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,47; 56,73</t>
+          <t>44,56; 57,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,81; 52,89</t>
+          <t>40,79; 52,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,5; 46,73</t>
+          <t>35,87; 46,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,08; 90,31</t>
+          <t>82,26; 89,49</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63,52%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>50,38%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44,78%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86,17%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>65,67%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>63,63%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>43,44%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>85,32%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>63,52%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>44,78%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,76; 73,98</t>
+          <t>54,6; 72,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51,46; 74,97</t>
+          <t>40,86; 58,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,03; 53,73</t>
+          <t>34,59; 54,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76,24; 91,09</t>
+          <t>77,14; 92,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53,46; 72,47</t>
+          <t>55,21; 73,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,8; 60,12</t>
+          <t>52,58; 73,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,24; 55,5</t>
+          <t>33,47; 54,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>76,25; 92,0</t>
+          <t>75,94; 90,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58,5; 70,94</t>
+          <t>57,45; 70,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,89; 63,0</t>
+          <t>47,99; 63,19</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37,21; 52,07</t>
+          <t>36,88; 51,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79,08; 90,16</t>
+          <t>78,98; 90,07</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33,57%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33,13%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>86,17%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>35,42%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>34,37%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>32,63%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>85,87%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,13%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,1; 38,76</t>
+          <t>32,55; 39,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,15; 38,02</t>
+          <t>30,39; 36,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,23; 35,73</t>
+          <t>29,71; 36,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,46; 88,5</t>
+          <t>83,76; 88,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,32; 39,2</t>
+          <t>32,15; 38,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,12; 36,87</t>
+          <t>30,84; 37,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,62; 36,24</t>
+          <t>29,68; 36,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>83,93; 88,57</t>
+          <t>84,15; 88,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,35; 38,0</t>
+          <t>33,25; 38,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,66; 36,24</t>
+          <t>31,64; 36,42</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,61; 35,49</t>
+          <t>30,77; 35,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,14; 87,93</t>
+          <t>84,53; 87,9</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>140</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10840</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12230</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20773</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>107169</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>19393</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>11779</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>15653</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>93955</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10840</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12230</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20773</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>121073</t>
+          <t>92780</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>215027</t>
+          <t>199950</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13519; 27061</t>
+          <t>6739; 17006</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7500; 17258</t>
+          <t>7624; 18406</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10778; 22813</t>
+          <t>14732; 27699</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88036; 98293</t>
+          <t>99655; 112260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6558; 16210</t>
+          <t>13829; 25753</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7745; 18205</t>
+          <t>7430; 17615</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14591; 28828</t>
+          <t>10630; 21785</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113895; 127313</t>
+          <t>86901; 96965</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22918; 38851</t>
+          <t>23242; 38638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17370; 32089</t>
+          <t>17227; 31546</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28311; 45091</t>
+          <t>27968; 45395</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>205166; 222729</t>
+          <t>191814; 207336</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>128</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24512</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21085</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32301</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82277</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>18093</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18013</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>26411</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>85240</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24512</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21085</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32301</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86163</t>
+          <t>86641</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>171404</t>
+          <t>168918</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12533; 24254</t>
+          <t>18843; 31086</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11823; 23953</t>
+          <t>15142; 27559</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20309; 34230</t>
+          <t>25562; 40233</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79721; 89104</t>
+          <t>75942; 86061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18217; 31334</t>
+          <t>12521; 24558</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15777; 28460</t>
+          <t>13048; 24448</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25253; 39985</t>
+          <t>19992; 33560</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80511; 90269</t>
+          <t>79951; 90932</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33877; 51688</t>
+          <t>34440; 52019</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30836; 47658</t>
+          <t>31146; 48690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49126; 68824</t>
+          <t>49050; 68579</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>163523; 177602</t>
+          <t>161061; 175611</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19808</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13338</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9915</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45384</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6540</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>14705</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8211</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>38229</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>19808</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13338</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9915</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49323</t>
+          <t>39008</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87552</t>
+          <t>84392</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3454; 11450</t>
+          <t>14177; 26953</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9840; 20436</t>
+          <t>8172; 19317</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4688; 13369</t>
+          <t>5894; 15115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31725; 42905</t>
+          <t>39378; 50194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13775; 26355</t>
+          <t>3291; 10954</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8551; 19284</t>
+          <t>9951; 20944</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5751; 15382</t>
+          <t>4776; 13584</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40386; 54473</t>
+          <t>32598; 44117</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19799; 34712</t>
+          <t>19429; 35046</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21335; 36548</t>
+          <t>21569; 36397</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12547; 25226</t>
+          <t>12574; 25682</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77994; 95476</t>
+          <t>77055; 92021</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>237</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43640</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47758</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>51180</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>175975</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>51258</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>47198</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>55775</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>181605</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>43640</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47758</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51180</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>192026</t>
+          <t>154066</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>373631</t>
+          <t>330040</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42422; 61022</t>
+          <t>35352; 53963</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38502; 57108</t>
+          <t>38385; 58626</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45258; 65227</t>
+          <t>41437; 61907</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163053; 195570</t>
+          <t>165438; 183698</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35132; 52971</t>
+          <t>41412; 60646</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37983; 57636</t>
+          <t>37927; 56702</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41474; 60468</t>
+          <t>45957; 65050</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>182370; 200048</t>
+          <t>146097; 160720</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81752; 108099</t>
+          <t>82433; 108391</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82194; 108703</t>
+          <t>81862; 108017</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93439; 120838</t>
+          <t>92829; 121860</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>353478; 389021</t>
+          <t>317808; 340585</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>160</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>43900</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>48679</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44394</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>124429</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>33588</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>37935</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>38725</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>107344</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>43900</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>48679</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44394</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>137804</t>
+          <t>106581</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>245148</t>
+          <t>231010</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27755; 40841</t>
+          <t>36406; 50624</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30508; 46005</t>
+          <t>40616; 57431</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30747; 47373</t>
+          <t>36732; 52730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101602; 112507</t>
+          <t>114974; 131771</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37638; 51285</t>
+          <t>27289; 41129</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40427; 56438</t>
+          <t>30509; 45473</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36329; 53066</t>
+          <t>31695; 47066</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>128050; 145172</t>
+          <t>100570; 111818</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68336; 87160</t>
+          <t>68470; 87825</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75680; 98082</t>
+          <t>75658; 98162</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71259; 93805</t>
+          <t>72002; 93696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>234331; 254727</t>
+          <t>219603; 238911</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>45981</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37304</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>30370</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>58845</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>49167</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>34305</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>26209</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>58783</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>45981</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>37304</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>30370</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>61529</t>
+          <t>59596</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>120312</t>
+          <t>118441</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41751; 55389</t>
+          <t>39528; 52426</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27744; 40417</t>
+          <t>30250; 43612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20532; 32416</t>
+          <t>23459; 37211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52524; 62754</t>
+          <t>52677; 63250</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38700; 52463</t>
+          <t>41336; 55216</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30950; 44511</t>
+          <t>28348; 39507</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23902; 37645</t>
+          <t>20194; 32986</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54905; 66241</t>
+          <t>53429; 64016</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86156; 104466</t>
+          <t>84597; 103836</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62557; 80606</t>
+          <t>61396; 80846</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47691; 66735</t>
+          <t>47264; 65833</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>111429; 127041</t>
+          <t>109503; 124880</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>805</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>180395</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>594079</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>178038</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>163934</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>170985</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>565157</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>188683</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>180395</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>188932</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>647916</t>
+          <t>538671</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1213073</t>
+          <t>1132751</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>161367; 194835</t>
+          <t>172022; 207056</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>148578; 181319</t>
+          <t>163273; 198567</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>153190; 187269</t>
+          <t>169393; 206176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>542711; 582449</t>
+          <t>577415; 609565</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>170832; 207188</t>
+          <t>161592; 195559</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>161831; 198110</t>
+          <t>147102; 181161</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>168905; 206654</t>
+          <t>155570; 189041</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>628852; 663625</t>
+          <t>523191; 551203</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>343905; 391851</t>
+          <t>342863; 392903</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>321149; 367570</t>
+          <t>320921; 369395</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>334985; 388354</t>
+          <t>336737; 386223</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1184200; 1237576</t>
+          <t>1108281; 1152492</t>
         </is>
       </c>
     </row>
